--- a/aq_files/0649.xlsx
+++ b/aq_files/0649.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="List_Basics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,468 +413,483 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Options</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Explanation</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>What command triggers a DAG manually?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>List is:</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>A) mutable B) immutable C) none D) both</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Use this command to manually start a DAG run.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>How do you list all DAGs from CLI?</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Index starts from:</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>A) 0 B) 1 C) -1 D) none</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>This shows all available DAGs.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What command shows task instances for a DAG?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Find running sum of array.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>This lists all tasks in a DAG.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>How do you clear task instances?</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Move zeroes to end.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Clears task states allowing re-execution.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What is the purpose of the backfill command?</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rotate list by k positions.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>airflow dags backfill runs DAG for past dates.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>How do you mark a task as successful?</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Find maximum subarray sum.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>This manually sets a task state to success.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What command unpauses a DAG?</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Find missing number in list.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>This enables scheduling for a DAG.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>How do you view logs for a task?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Check sorted list.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>This displays task execution logs.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What does the "run_id" represent?</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reverse list in-place.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Run ID uniquely identifies a DAG run.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Scenario: A task failed due to a transient error. How to retry without rerunning dependencies?</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Find pair with target sum.</t>
+          <t>Scenario-based</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>A) Clear only that task,B) Clear entire DAG,C) Restart scheduler,D) Delete DAG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Clearing a single task retries just that task.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What is the purpose of the "--conf" parameter in trigger command?</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Remove element from list.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Passes configuration JSON to the DAG run.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>How do you run a task from CLI?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Find intersection of sorted lists.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Use test command to run a task locally.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What is the difference between test and run commands?</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Find longest increasing subsequence (basic).</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Test doesn't record state; run does.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>How do you check scheduler health?</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Split list into chunks.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>This shows if the scheduler is running.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What command generates a DAG visualization?</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Flatten nested list.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>This generates a PNG of the DAG structure.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>How do you list active DAG runs?</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Find first non-repeating element.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>This shows current and recent DAG runs.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What is the command to start all Airflow services in development?</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Check if list contains duplicates.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Standalone mode runs all services in one process.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Scenario: A production DAG is stuck. What's the first CLI command to debug?</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Merge sorted lists.</t>
+          <t>Scenario-based</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>A) airflow dags list-runs --dag-id,B) airflow tasks clear,C) airflow db reset,D) airflow webserver</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Checking DAG run status helps identify the issue.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>How do you pause a DAG from CLI?</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Find peak element.</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>This stops scheduling of the DAG.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What command validates all DAGs for syntax errors?</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Find subarray with given sum.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>This shows import errors in DAG files.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
